--- a/other/covid_plasma_donation_form.xlsx
+++ b/other/covid_plasma_donation_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'no_condition'}</t>
+          <t>no_condition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'No Condition'}</t>
+          <t>No Condition</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'condition_1'}</t>
+          <t>condition_1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Condition 1'}</t>
+          <t>Condition 1</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'condition_2'}</t>
+          <t>condition_2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Condition 2'}</t>
+          <t>Condition 2</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ab'}</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'AB'}</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'o'}</t>
+          <t>o</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'O'}</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
